--- a/src/DashboardApp/hash_table.xlsx
+++ b/src/DashboardApp/hash_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,1446 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>158.1650463801035</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>140.4793494548849</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>119.3668302616216</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118.9920177595465</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118.036912105332</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118.0166784913146</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>117.9316255663383</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>115.9706916035457</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113.5549757650904</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111.0585111527221</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110.7599537022703</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>108.0790972219922</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>104.2212221821215</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104.1878267136136</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>104.0571834712687</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104.0404203957858</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>104.0183537709018</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>103.6147249579245</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>103.5141944662491</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>103.5100378161867</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>100.1008992124274</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>99.88042148375648</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>99.33879185119594</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>98.61445422086464</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>95.65585002967177</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>94.17035066844453</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>89.64406671444854</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>87.53503658362602</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>87.21488573857158</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>87.09682226049139</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>87.08008387620227</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>86.7447404111212</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>86.71556506357494</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>86.23053519236365</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>86.19160892051926</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>85.84940939934279</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>85.84010520302175</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>85.83890400112267</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>85.80460782179057</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>85.80226103247921</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>85.41046177446411</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>85.40926306106505</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>85.32129470414137</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>84.58861301803108</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>84.45294476330498</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>84.45173589405893</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>83.77121078265957</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>75.34986600329692</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>74.06579899191482</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>72.96743609780836</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>72.50560116949372</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>72.48730665055778</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>71.52752114811501</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>71.22402851834319</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>71.22207101901665</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>63.6369388034574</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>61.45952628842824</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>61.35333303061934</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>61.34729094538223</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60.82150797854977</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60.82078971182391</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>60.77672424253744</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>60.77423331359974</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>60.52652574704242</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>60.51563644296317</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>59.48819672008609</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>58.91979468833282</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>57.97216749720803</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>57.97177839536398</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>56.96959454940236</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>56.9098004414563</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>56.8837727817519</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>56.4772624158752</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>56.47643679988512</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>56.39963746903088</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>55.84715533812479</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>55.84632666870497</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>55.57355927847324</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>55.52180975023741</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>55.29179503502263</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>55.29095509161613</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>55.25029022506039</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>55.24927688633537</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>55.04328306310995</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>54.93147639172844</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>54.91491015618109</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>52.65127167179818</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>52.34426192459142</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>52.09107794647971</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>52.09049282588706</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>51.65321864199844</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>51.6460718937924</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>51.48050080399078</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>51.09995909409491</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>51.09985036293892</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>51.00566202934783</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>51.0038272970389</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>50.7247218236779</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>50.71446769206425</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>50.58962627834663</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>49.98600887780673</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>49.95846814405213</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>49.59412372347759</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>49.59272401751318</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>49.3136830778272</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>48.99442442520443</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>48.81253722345948</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>48.38708927328864</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>48.3856912111647</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>48.24474675373118</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>48.21518825939027</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>47.3828327212194</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>47.16450317520631</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>47.16378256687458</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>47.14989648325469</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>46.73360539542289</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>46.7221839859568</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>46.71215201428696</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>46.66778145414288</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>46.20529802361622</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>46.19260418339047</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>46.18757613860151</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>46.18685288297866</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>46.08306903151487</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>46.06721127675289</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>46.06570815208594</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>46.00416260795986</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>45.88489854387943</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>45.88416495531743</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>45.61576319174895</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>45.50513268808658</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>45.39065198621006</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>44.98479329875995</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>44.97209918171004</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>44.83226435125977</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>44.81870654010052</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>44.78666419603462</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>44.77634188067296</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>44.27204698126776</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>44.13756178852925</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>43.85408607987592</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>43.84752562644493</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>43.71091207231369</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>43.71003321564334</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>43.57349490266771</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>42.3612752439641</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>42.1931241884006</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>42.13673871869489</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>41.77982935106288</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>41.68368550040984</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>41.68298210999572</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>41.38222007483981</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>41.38144605294234</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>41.24582692493893</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>40.73037655793892</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>40.72964389977154</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>40.61581323795715</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>40.44517200785226</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>40.44444765314761</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>38.08866383316067</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>37.90095843170418</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>37.59002305336626</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>37.45435129715281</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>37.20060413702405</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>37.19849601747077</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>37.17564367290004</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>37.17491253687244</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>36.7353276646313</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>35.92621294205117</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>35.31170927063887</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>35.24838351237778</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>35.13778422663728</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>35.12786997630884</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>34.80423891459146</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>34.79863853649483</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>34.22661373716899</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>33.69624698744796</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>33.6332276956378</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>33.3760809632688</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>33.28494992526429</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>33.22985051122621</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>32.92286458542477</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>32.8359830036208</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>32.83476755355916</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>32.83258138116746</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>32.70594636993432</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>32.49022475613583</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>32.34833898852064</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>32.03085661431304</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>32.03018088652498</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>31.99322646477615</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>31.89705472813002</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>31.89641703987679</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>31.89424898727441</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>31.89361832582316</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/DashboardApp/hash_table.xlsx
+++ b/src/DashboardApp/hash_table.xlsx
@@ -437,27 +437,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>158.1650463801035</v>
+        <v>146.9522454109647</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>140.4793494548849</v>
+        <v>134.7227926633763</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119.3668302616216</v>
+        <v>122.3696610208511</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118.9920177595465</v>
+        <v>119.3668302616215</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118.036912105332</v>
+        <v>118.9920177595466</v>
       </c>
     </row>
     <row r="7">
@@ -472,702 +472,702 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115.9706916035457</v>
+        <v>115.9735189418405</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113.5549757650904</v>
+        <v>115.9706916035452</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111.0585111527221</v>
+        <v>113.7185809842237</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110.7599537022703</v>
+        <v>113.5549757650911</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108.0790972219922</v>
+        <v>110.7578963371989</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104.2212221821215</v>
+        <v>109.8504572502239</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104.1878267136136</v>
+        <v>109.8483881890557</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104.0571834712687</v>
+        <v>108.5032624508844</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104.0404203957858</v>
+        <v>108.079097221993</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104.0183537709018</v>
+        <v>104.2212221821213</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103.6147249579245</v>
+        <v>104.1878267136136</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103.5141944662491</v>
+        <v>104.0404203957855</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103.5100378161867</v>
+        <v>104.0183537709018</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>100.1008992124274</v>
+        <v>103.6147249579247</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>99.88042148375648</v>
+        <v>103.5141944662492</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>99.33879185119594</v>
+        <v>103.5100378161867</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>98.61445422086464</v>
+        <v>102.0879926511303</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>95.65585002967177</v>
+        <v>100.1008992124278</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>94.17035066844453</v>
+        <v>99.88042148375671</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>89.64406671444854</v>
+        <v>99.33879185119631</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>87.53503658362602</v>
+        <v>98.61693960618288</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>87.21488573857158</v>
+        <v>98.61445422086464</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>87.09682226049139</v>
+        <v>98.58396436348401</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>87.08008387620227</v>
+        <v>98.25972113653546</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>86.7447404111212</v>
+        <v>95.65585002967191</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>86.71556506357494</v>
+        <v>94.32421554746446</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>86.23053519236365</v>
+        <v>94.17035066844427</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>86.19160892051926</v>
+        <v>89.27234296477734</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>85.84940939934279</v>
+        <v>89.13902951421824</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>85.84010520302175</v>
+        <v>87.53503658362584</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>85.83890400112267</v>
+        <v>87.21488573857178</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>85.80460782179057</v>
+        <v>87.20952725436959</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>85.80226103247921</v>
+        <v>87.09682226049135</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>85.41046177446411</v>
+        <v>87.08008387620227</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>85.40926306106505</v>
+        <v>86.71556506357501</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>85.32129470414137</v>
+        <v>86.23053519236348</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>84.58861301803108</v>
+        <v>86.20610919072003</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>84.45294476330498</v>
+        <v>86.19160892051897</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>84.45173589405893</v>
+        <v>85.84940939934246</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>83.77121078265957</v>
+        <v>85.84010520302178</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>75.34986600329692</v>
+        <v>85.8389040011227</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>74.06579899191482</v>
+        <v>85.802261032479</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>72.96743609780836</v>
+        <v>85.41046177446408</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>72.50560116949372</v>
+        <v>85.40926306106489</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>72.48730665055778</v>
+        <v>85.32129470414137</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>71.52752114811501</v>
+        <v>84.58861301803127</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>71.22402851834319</v>
+        <v>84.45294476330498</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>71.22207101901665</v>
+        <v>84.45173589405887</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>63.6369388034574</v>
+        <v>83.77121078265925</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>61.45952628842824</v>
+        <v>75.54569743080293</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>61.35333303061934</v>
+        <v>74.06579899191482</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>61.34729094538223</v>
+        <v>72.96743609780836</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60.82150797854977</v>
+        <v>72.50755214156295</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>60.82078971182391</v>
+        <v>72.50560116949357</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>60.77672424253744</v>
+        <v>72.48730665055764</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>60.77423331359974</v>
+        <v>72.24228304834109</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>60.52652574704242</v>
+        <v>72.11852578992045</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>60.51563644296317</v>
+        <v>71.52752114811497</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>59.48819672008609</v>
+        <v>71.22402851834319</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>58.91979468833282</v>
+        <v>71.22207101901665</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>57.97216749720803</v>
+        <v>63.63693880345778</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>57.97177839536398</v>
+        <v>61.45952628842824</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>56.96959454940236</v>
+        <v>61.3533330306194</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>56.9098004414563</v>
+        <v>61.34729094538223</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>56.8837727817519</v>
+        <v>60.82150797854977</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>56.4772624158752</v>
+        <v>60.82078971182391</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>56.47643679988512</v>
+        <v>60.77672424253763</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>56.39963746903088</v>
+        <v>60.77423331359998</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>55.84715533812479</v>
+        <v>60.52652574704242</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>55.84632666870497</v>
+        <v>60.51563644296317</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>55.57355927847324</v>
+        <v>59.48819672008593</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>55.52180975023741</v>
+        <v>56.96959454940236</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>55.29179503502263</v>
+        <v>56.88377278175268</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>55.29095509161613</v>
+        <v>56.4772624158752</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>55.25029022506039</v>
+        <v>56.47643679988514</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>55.24927688633537</v>
+        <v>56.39963746903088</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>55.04328306310995</v>
+        <v>55.84715533812496</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>54.93147639172844</v>
+        <v>55.84632666870497</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>54.91491015618109</v>
+        <v>55.57355927847324</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>52.65127167179818</v>
+        <v>55.50170466062593</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>52.34426192459142</v>
+        <v>55.29179503502275</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>52.09107794647971</v>
+        <v>55.29095509161613</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>52.09049282588706</v>
+        <v>55.24927688633538</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>51.65321864199844</v>
+        <v>55.0432830631098</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>51.6460718937924</v>
+        <v>55.03750475316465</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>51.48050080399078</v>
+        <v>54.91491015618076</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>51.09995909409491</v>
+        <v>53.59858580102114</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>51.09985036293892</v>
+        <v>52.34485899223492</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>51.00566202934783</v>
+        <v>52.3442619245915</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>51.0038272970389</v>
+        <v>51.65321864199844</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>50.7247218236779</v>
+        <v>51.6460718937924</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>50.71446769206425</v>
+        <v>51.48050080399052</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>50.58962627834663</v>
+        <v>51.09995909409491</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>49.98600887780673</v>
+        <v>51.09985036293892</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>49.95846814405213</v>
+        <v>51.00566202934783</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>49.59412372347759</v>
+        <v>51.00382729703911</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>49.59272401751318</v>
+        <v>50.87989176062561</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>49.3136830778272</v>
+        <v>50.72472182367785</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>48.99442442520443</v>
+        <v>50.71446769206375</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>48.81253722345948</v>
+        <v>50.5896262783463</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>48.38708927328864</v>
+        <v>49.95846814405213</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>48.3856912111647</v>
+        <v>49.91012341200933</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>48.24474675373118</v>
+        <v>49.59272401751328</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>48.21518825939027</v>
+        <v>49.31368307782754</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>47.3828327212194</v>
+        <v>48.99442442520453</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>47.16450317520631</v>
+        <v>48.81113549548446</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>47.16378256687458</v>
+        <v>48.38569121116468</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>47.14989648325469</v>
+        <v>48.2151882593903</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>46.73360539542289</v>
+        <v>47.16450317520631</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>46.7221839859568</v>
+        <v>47.16378256687458</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>46.71215201428696</v>
+        <v>47.14989648325469</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>46.66778145414288</v>
+        <v>46.75771388504589</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>46.20529802361622</v>
+        <v>46.73572992304257</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>46.19260418339047</v>
+        <v>46.71215201428696</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>46.18757613860151</v>
+        <v>46.66778145414294</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>46.18685288297866</v>
+        <v>46.20529802361622</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>46.08306903151487</v>
+        <v>46.19260418339047</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>46.06721127675289</v>
+        <v>46.18757613860151</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>46.06570815208594</v>
+        <v>46.18685288297866</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>46.00416260795986</v>
+        <v>46.08306903151487</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>45.88489854387943</v>
+        <v>46.06721127675289</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>45.88416495531743</v>
+        <v>46.06570815208594</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>45.61576319174895</v>
+        <v>46.00416260795973</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>45.50513268808658</v>
+        <v>45.88489854387943</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>45.39065198621006</v>
+        <v>45.88416495531743</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>44.98479329875995</v>
+        <v>45.61576319174895</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>44.97209918171004</v>
+        <v>45.50513268808658</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>44.83226435125977</v>
+        <v>45.40697296102377</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>44.81870654010052</v>
+        <v>45.39065198621034</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>44.78666419603462</v>
+        <v>44.83226435126005</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>44.77634188067296</v>
+        <v>44.81870654010052</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>44.27204698126776</v>
+        <v>44.78666419603439</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>44.13756178852925</v>
+        <v>44.27975738195504</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>43.85408607987592</v>
+        <v>44.27204698126776</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>43.84752562644493</v>
+        <v>44.1375617885294</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>43.71091207231369</v>
+        <v>43.85408607987592</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>43.71003321564334</v>
+        <v>43.84752562644493</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>43.57349490266771</v>
+        <v>43.71091207231374</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>42.3612752439641</v>
+        <v>43.71003321564334</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>42.1931241884006</v>
+        <v>42.19382281025711</v>
       </c>
     </row>
     <row r="149">
@@ -1177,312 +1177,312 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>41.77982935106288</v>
+        <v>41.77982935106247</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>41.68368550040984</v>
+        <v>41.68298210999572</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>41.68298210999572</v>
+        <v>41.38144605294234</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>41.38222007483981</v>
+        <v>41.24582692493904</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>41.38144605294234</v>
+        <v>40.73037655793892</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>41.24582692493893</v>
+        <v>40.72964389977154</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>40.73037655793892</v>
+        <v>40.6158132379574</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>40.72964389977154</v>
+        <v>40.44517200785226</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>40.61581323795715</v>
+        <v>40.44444765314761</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>40.44517200785226</v>
+        <v>39.00318136266564</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>40.44444765314761</v>
+        <v>39.00063883840279</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>38.08866383316067</v>
+        <v>38.08866383316072</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>37.90095843170418</v>
+        <v>37.9153048192415</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>37.59002305336626</v>
+        <v>37.90095843170418</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>37.45435129715281</v>
+        <v>37.59002305336626</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>37.20060413702405</v>
+        <v>37.45435129715298</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>37.19849601747077</v>
+        <v>37.20060413702405</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>37.17564367290004</v>
+        <v>37.19849601747077</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>37.17491253687244</v>
+        <v>37.17564367290004</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>36.7353276646313</v>
+        <v>37.17491253687244</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>35.92621294205117</v>
+        <v>36.75796536899655</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>35.31170927063887</v>
+        <v>36.75746411205269</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>35.24838351237778</v>
+        <v>36.73584471376965</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>35.13778422663728</v>
+        <v>36.7353276646313</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>35.12786997630884</v>
+        <v>36.50717994095338</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>34.80423891459146</v>
+        <v>36.21585224721525</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>34.79863853649483</v>
+        <v>36.20554862382762</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>34.22661373716899</v>
+        <v>35.92621294205117</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>33.69624698744796</v>
+        <v>35.91703292152041</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>33.6332276956378</v>
+        <v>35.31170927063948</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>33.3760809632688</v>
+        <v>35.25492902591257</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>33.28494992526429</v>
+        <v>35.24838351237778</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>33.22985051122621</v>
+        <v>35.1377842266371</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>32.92286458542477</v>
+        <v>35.12786997630884</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>32.8359830036208</v>
+        <v>34.87741175950249</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>32.83476755355916</v>
+        <v>34.80423891459146</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>32.83258138116746</v>
+        <v>34.79863853649483</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>32.70594636993432</v>
+        <v>34.22661373716899</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>32.49022475613583</v>
+        <v>34.12774421803709</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>32.34833898852064</v>
+        <v>34.06691321916965</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>32.03085661431304</v>
+        <v>33.69685479856102</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>32.03018088652498</v>
+        <v>33.69624698744808</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>31.99322646477615</v>
+        <v>33.63322769563782</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>31.89705472813002</v>
+        <v>33.3760809632688</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>31.89641703987679</v>
+        <v>33.28616831621833</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>31.89424898727441</v>
+        <v>33.28494992526429</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>31.89361832582316</v>
+        <v>33.22985051122621</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>-1</v>
+        <v>32.92286458542492</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>-1</v>
+        <v>32.83598300362131</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>-1</v>
+        <v>32.83476755355916</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>-1</v>
+        <v>32.83258138116746</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>-1</v>
+        <v>32.70662030183775</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>-1</v>
+        <v>32.70594636993447</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>-1</v>
+        <v>32.49022475613583</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>-1</v>
+        <v>32.34833898852064</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>-1</v>
+        <v>32.03085661431294</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>-1</v>
+        <v>32.03018088652488</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>-1</v>
+        <v>31.99322646477615</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>-1</v>
+        <v>31.89705472813011</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>-1</v>
+        <v>31.89641703987679</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>-1</v>
+        <v>31.89424898727446</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>-1</v>
+        <v>31.89361832582329</v>
       </c>
     </row>
     <row r="212">

--- a/src/DashboardApp/hash_table.xlsx
+++ b/src/DashboardApp/hash_table.xlsx
@@ -437,1052 +437,1052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>146.9522454109647</v>
+        <v>18.6144625992209</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134.7227926633763</v>
+        <v>16.43512253136544</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122.3696610208511</v>
+        <v>15.77900665531947</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119.3668302616215</v>
+        <v>14.66410218309929</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118.9920177595466</v>
+        <v>13.3447267903799</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118.0166784913146</v>
+        <v>12.44995122914663</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117.9316255663383</v>
+        <v>8.240447025363707</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115.9735189418405</v>
+        <v>7.908005312866873</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115.9706916035452</v>
+        <v>7.778152495954949</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113.7185809842237</v>
+        <v>7.665195775008982</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113.5549757650911</v>
+        <v>7.542073792847603</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110.7578963371989</v>
+        <v>7.251568631278382</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109.8504572502239</v>
+        <v>7.100437277068083</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109.8483881890557</v>
+        <v>7.024423915842871</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>108.5032624508844</v>
+        <v>6.700222752642437</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>108.079097221993</v>
+        <v>6.679901416981259</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104.2212221821213</v>
+        <v>6.297195687874957</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104.1878267136136</v>
+        <v>6.232889988004087</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104.0404203957855</v>
+        <v>6.078610417987607</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104.0183537709018</v>
+        <v>6.073739126008116</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103.6147249579247</v>
+        <v>5.601896270963658</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103.5141944662492</v>
+        <v>5.288815940683255</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103.5100378161867</v>
+        <v>5.245654095095698</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102.0879926511303</v>
+        <v>5.104770821357563</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>100.1008992124278</v>
+        <v>5.03640892447712</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>99.88042148375671</v>
+        <v>5.021573723728667</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>99.33879185119631</v>
+        <v>4.924888436226138</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>98.61693960618288</v>
+        <v>4.91891351310707</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>98.61445422086464</v>
+        <v>4.904649436675812</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>98.58396436348401</v>
+        <v>4.888685947150639</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>98.25972113653546</v>
+        <v>4.831524459184755</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>95.65585002967191</v>
+        <v>4.814396056529979</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>94.32421554746446</v>
+        <v>4.813943547329447</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>94.17035066844427</v>
+        <v>4.736889059669314</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>89.27234296477734</v>
+        <v>4.726224018944181</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>89.13902951421824</v>
+        <v>4.722595506367155</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>87.53503658362584</v>
+        <v>4.71218879506925</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>87.21488573857178</v>
+        <v>4.712185627406562</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>87.20952725436959</v>
+        <v>4.707771730101995</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>87.09682226049135</v>
+        <v>4.687572527072725</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>87.08008387620227</v>
+        <v>4.685691472398901</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>86.71556506357501</v>
+        <v>4.669201329720174</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>86.23053519236348</v>
+        <v>4.604261815148591</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>86.20610919072003</v>
+        <v>4.604259769292196</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>86.19160892051897</v>
+        <v>4.49506888472706</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>85.84940939934246</v>
+        <v>4.46061635483932</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>85.84010520302178</v>
+        <v>4.452695169918464</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>85.8389040011227</v>
+        <v>4.452269003190468</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>85.802261032479</v>
+        <v>4.452265614177953</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>85.41046177446408</v>
+        <v>4.449494715575342</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>85.40926306106489</v>
+        <v>4.446725358595827</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>85.32129470414137</v>
+        <v>4.432364585717341</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>84.58861301803127</v>
+        <v>4.418143663341567</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>84.45294476330498</v>
+        <v>4.404089826112356</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>84.45173589405887</v>
+        <v>4.388291517533238</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>83.77121078265925</v>
+        <v>4.388291517533216</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>75.54569743080293</v>
+        <v>4.388291517533216</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>74.06579899191482</v>
+        <v>4.388291517533216</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>72.96743609780836</v>
+        <v>4.388291517533194</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>72.50755214156295</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>72.50560116949357</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>72.48730665055764</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>72.24228304834109</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>72.11852578992045</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>71.52752114811497</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>71.22402851834319</v>
+        <v>4.388291517533127</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>71.22207101901665</v>
+        <v>4.349633931007113</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>63.63693880345778</v>
+        <v>4.349633931007091</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>61.45952628842824</v>
+        <v>4.349633931007069</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>61.3533330306194</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>61.34729094538223</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>60.82150797854977</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>60.82078971182391</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>60.77672424253763</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>60.77423331359998</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>60.52652574704242</v>
+        <v>4.349633931007024</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>60.51563644296317</v>
+        <v>4.349633931007024</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>59.48819672008593</v>
+        <v>4.349633931007024</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>56.96959454940236</v>
+        <v>4.349633931007002</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>56.88377278175268</v>
+        <v>4.34963393100698</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>56.4772624158752</v>
+        <v>4.34963393100698</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>56.47643679988514</v>
+        <v>4.335477316788561</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>56.39963746903088</v>
+        <v>4.335475298823388</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>55.84715533812496</v>
+        <v>4.325966886632249</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>55.84632666870497</v>
+        <v>4.270257231299013</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>55.57355927847324</v>
+        <v>4.254097306094673</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>55.50170466062593</v>
+        <v>4.23344250423825</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>55.29179503502275</v>
+        <v>4.233442504238227</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>55.29095509161613</v>
+        <v>4.233442504238227</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>55.24927688633538</v>
+        <v>4.233442504238227</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>55.0432830631098</v>
+        <v>4.233442504238227</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>55.03750475316465</v>
+        <v>4.233442504238227</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>54.91491015618076</v>
+        <v>4.233442504238183</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>53.59858580102114</v>
+        <v>4.233442504238161</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>52.34485899223492</v>
+        <v>4.233442504238139</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>52.3442619245915</v>
+        <v>4.233442504238139</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>51.65321864199844</v>
+        <v>4.233442504238094</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>51.6460718937924</v>
+        <v>4.219070660454505</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>51.48050080399052</v>
+        <v>4.194067920212374</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>51.09995909409491</v>
+        <v>4.175848843858931</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>51.09985036293892</v>
+        <v>4.169529680102513</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>51.00566202934783</v>
+        <v>4.168259217128245</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>51.00382729703911</v>
+        <v>4.16099973736932</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>50.87989176062561</v>
+        <v>4.152707281016221</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>50.72472182367785</v>
+        <v>4.139113523896243</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>50.71446769206375</v>
+        <v>4.11804620363041</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>50.5896262783463</v>
+        <v>4.061116337551218</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>49.95846814405213</v>
+        <v>4.00797224759124</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>49.91012341200933</v>
+        <v>4.000000000000048</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>49.59272401751328</v>
+        <v>4.000000000000048</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>49.31368307782754</v>
+        <v>4.000000000000048</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>48.99442442520453</v>
+        <v>4.000000000000048</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>48.81113549548446</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>48.38569121116468</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>48.2151882593903</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>47.16450317520631</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>47.16378256687458</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>47.14989648325469</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>46.75771388504589</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>46.73572992304257</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>46.71215201428696</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>46.66778145414294</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>46.20529802361622</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>46.19260418339047</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>46.18757613860151</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>46.18685288297866</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>46.08306903151487</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>46.06721127675289</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>46.06570815208594</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>46.00416260795973</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>45.88489854387943</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>45.88416495531743</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>45.61576319174895</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>45.50513268808658</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>45.40697296102377</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>45.39065198621034</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>44.83226435126005</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>44.81870654010052</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>44.78666419603439</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>44.27975738195504</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>44.27204698126776</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>44.1375617885294</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>43.85408607987592</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>43.84752562644493</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>43.71091207231374</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>43.71003321564334</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>42.19382281025711</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>42.13673871869489</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>41.77982935106247</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>41.68298210999572</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>41.38144605294234</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>41.24582692493904</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>40.73037655793892</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>40.72964389977154</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>40.6158132379574</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>40.44517200785226</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>40.44444765314761</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>39.00318136266564</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>39.00063883840279</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>38.08866383316072</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>37.9153048192415</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>37.90095843170418</v>
+        <v>3.999999999999937</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>37.59002305336626</v>
+        <v>3.999999999999937</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>37.45435129715298</v>
+        <v>3.999999999999937</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>37.20060413702405</v>
+        <v>3.999999999999937</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>37.19849601747077</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>37.17564367290004</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>37.17491253687244</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>36.75796536899655</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>36.75746411205269</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>36.73584471376965</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>36.7353276646313</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>36.50717994095338</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>36.21585224721525</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>36.20554862382762</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>35.92621294205117</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>35.91703292152041</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>35.31170927063948</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>35.25492902591257</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>35.24838351237778</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>35.1377842266371</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>35.12786997630884</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>34.87741175950249</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>34.80423891459146</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>34.79863853649483</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>34.22661373716899</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>34.12774421803709</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>34.06691321916965</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>33.69685479856102</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>33.69624698744808</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>33.63322769563782</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>33.3760809632688</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>33.28616831621833</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>33.28494992526429</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>33.22985051122621</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>32.92286458542492</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>32.83598300362131</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>32.83476755355916</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>32.83258138116746</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>32.70662030183775</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>32.70594636993447</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>32.49022475613583</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>32.34833898852064</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>32.03085661431294</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>32.03018088652488</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>31.99322646477615</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>31.89705472813011</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>31.89641703987679</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>31.89424898727446</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>31.89361832582329</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="212">

--- a/src/DashboardApp/hash_table.xlsx
+++ b/src/DashboardApp/hash_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,1446 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>24.30731921307373</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>22.86600961511795</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>18.83187548348985</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>18.6144625992209</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>17.36819739724094</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>17.02360507988341</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>16.55407615166203</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>16.43512253136544</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>15.77900665531947</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>15.54531838293443</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>14.66410218309929</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>13.3447267903799</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12.44995122914663</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11.45377185083114</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>10.65512917904204</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9.500031717086577</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8.913627025534243</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8.799274107140009</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8.335508550897774</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8.275535183571348</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8.254373206547704</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8.240447025363707</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>8.216112360289962</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7.908005312866873</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.788605641411117</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.778152495954949</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7.665195775008982</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7.542073792847603</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>7.378868840111763</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>7.251568631278382</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>7.100437277068083</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>7.024423915842871</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6.73650542439198</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6.700222752642437</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>6.679901416981259</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6.633690869228259</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>6.338943322872359</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>6.297195687874957</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>6.232889988004087</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>6.078610417987607</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>6.073739126008116</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5.601896270963658</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5.288815940683255</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>5.245654095095698</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5.230808144247701</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.104770821357563</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>5.104767181518222</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>5.0586650418176</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>5.041536772765931</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>5.03640892447712</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>5.021573723728667</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4.952326044590071</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4.924888436226138</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4.91891351310707</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4.916023145354398</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4.916017807544404</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4.906387217104968</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4.904649436675812</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4.888685947150639</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>4.831524459184755</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4.814396056529979</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4.813943547329447</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4.795308242662988</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4.736889059669314</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>4.736883734731001</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>4.726224018944181</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4.722595506367155</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4.719857205414435</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>4.71218879506925</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>4.712185627406562</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>4.70926335620534</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4.707771730101995</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4.687572527072725</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4.685691472398901</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4.685687162808527</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>4.669201329720174</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>4.604261815148591</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4.604259769292196</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4.49506888472706</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4.480265097013403</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4.475571792297295</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>4.46061635483932</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>4.452695169918464</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4.452269003190468</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>4.452265614177953</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>4.449494715575342</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4.44672724950923</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4.446725358595827</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>4.432364585717341</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>4.429826105328005</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>4.418143663341567</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4.404089826112356</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4.38829151753326</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>4.349633931007113</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>4.349633931007091</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>4.335477316788561</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>4.335475298823388</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>4.325966886632249</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>4.274519009916911</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>4.270257231299013</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>4.254097306094673</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>4.233442504238094</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>4.219071160432186</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>4.219070660454505</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>4.194067920212374</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>4.175848843858931</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>4.169529680102513</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>4.168261095111214</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>4.168259217128245</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>4.16099973736932</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>4.152707281016221</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>4.139113523896243</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>4.11804620363041</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>4.061116337551218</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>4.00797224759124</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/DashboardApp/hash_table.xlsx
+++ b/src/DashboardApp/hash_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,1446 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>22.86600961511795</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>17.36819739724094</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>17.02360507988341</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16.55407615166203</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16.43512253136544</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>15.77900665531947</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>15.54531838293443</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>14.66410218309929</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>13.3447267903799</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>12.44995122914663</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11.45377185083114</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10.65512917904204</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8.913627025534243</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8.335508550897774</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8.275535183571348</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7.908005312866873</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7.778152495954949</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7.665195775008982</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7.542073792847603</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7.378868840111763</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7.251568631278382</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7.024423915842871</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6.73650542439198</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6.700222752642437</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>6.679901416981259</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6.633690869228259</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6.338943322872359</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>6.297195687874957</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6.232889988004087</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>6.078610417987607</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6.073739126008116</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>5.601896270963658</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>5.288815940683255</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>5.245654095095698</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5.230808144247701</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5.104770821357563</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5.104767181518222</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>5.0586650418176</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5.03640892447712</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>5.021573723728667</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4.924888436226138</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4.91891351310707</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4.916023145354398</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4.904649436675812</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.888685947150639</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4.831524459184755</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4.814396056529979</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4.813943547329447</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4.736889059669314</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4.726224018944181</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>4.722595506367155</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4.719857205414435</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4.71218879506925</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4.712185627406562</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4.70926335620534</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4.707771730101995</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4.687572527072725</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4.685691472398901</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4.669201329720174</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>4.604261815148591</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4.604259769292196</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4.49506888472706</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4.480265097013403</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4.475571792297295</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>4.46061635483932</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>4.452695169918464</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4.452269003190468</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4.452265614177953</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>4.449494715575342</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>4.44672724950923</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>4.446725358595827</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4.432364585717341</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4.429826105328005</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4.418143663341567</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4.404089826112356</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>4.38829151753326</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>4.349633931007113</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>4.349633931007091</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>4.335477316788561</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>4.335475298823388</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>4.325966886632249</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>4.274519009916911</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>4.270257231299013</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>4.233442504238094</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>4.219071160432186</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>4.194067920212374</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>4.175848843858931</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>4.169529680102513</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>4.168261095111214</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>4.168259217128245</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>4.16099973736932</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>4.152707281016221</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>4.139113523896243</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>4.11804620363041</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>4.061116337551218</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>4.00797224759124</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/DashboardApp/hash_table.xlsx
+++ b/src/DashboardApp/hash_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,1446 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>24.30731921307373</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>22.86600961511795</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>18.83187548348985</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>18.6144625992209</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>17.36819739724094</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>17.02360507988341</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>16.43512253136544</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>15.77900665531947</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>15.54531838293443</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.66410218309929</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>13.3447267903799</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12.44995122914663</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11.45377185083114</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10.40744226314052</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9.500031717086577</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8.913627025534243</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8.799274107140009</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8.335508550897774</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8.275535183571348</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8.254373206547704</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8.240447025363707</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7.908005312866873</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7.788605641411117</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7.778152495954949</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.665195775008982</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.542073792847603</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7.378868840111763</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7.251568631278382</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>7.100437277068083</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>7.024423915842871</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6.73650542439198</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6.679901416981259</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6.633690869228259</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6.338943322872359</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>6.297195687874957</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6.232889988004087</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>6.078610417987607</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>6.073739126008116</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5.601896270963658</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>5.288815940683255</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5.245654095095698</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5.230808144247701</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5.104770821357563</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>5.104767181518222</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5.0586650418176</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.041536772765931</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>5.03640892447712</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>5.021573723728667</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4.952326044590071</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4.924888436226138</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>4.91891351310707</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4.916023145354398</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4.916017807544404</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4.906387217104968</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4.904649436675812</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4.888685947150639</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4.831524459184755</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4.814396056529979</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4.813943547329447</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>4.795308242662988</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4.736889059669314</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4.736883734731001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4.726224018944181</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4.722595506367155</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>4.719857205414435</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>4.71218879506925</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4.712185627406562</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4.70926335620534</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>4.707771730101995</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>4.698819438089386</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>4.687572527072725</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4.685691472398901</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4.685687162808527</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4.669201329720174</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4.604261815148591</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>4.604259769292196</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>4.49506888472706</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4.480265097013403</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4.480258734680631</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4.475571792297295</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4.46061635483932</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>4.452695169918464</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>4.452269003190468</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4.452265614177953</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>4.449494715575342</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>4.44672724950923</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4.446725358595827</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4.432364585717341</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>4.429826105328005</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>4.418143663341567</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>4.404089826112356</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>4.349633931007113</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4.349633931007091</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>4.335477316788561</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>4.335475298823388</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>4.325966886632249</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>4.274519009916911</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>4.270257231299013</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>4.254097306094673</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>4.233442504238094</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>4.219071160432186</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>4.219070660454505</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>4.194067920212374</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>4.175848843858931</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>4.169529680102513</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>4.168261095111214</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>4.168259217128245</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>4.16099973736932</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>4.152707281016221</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>4.139113523896243</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>4.11804620363041</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>4.061116337551218</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>4.00797224759124</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/DashboardApp/hash_table.xlsx
+++ b/src/DashboardApp/hash_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,1446 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>24.30731921307375</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>22.8660096151181</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>21.64736113255658</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>17.36819739724072</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>17.02360507988355</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>16.55407615166182</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>16.43512253136532</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>15.77900665531933</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>15.54531838293467</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.66410218309932</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>13.34472679038007</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12.44995122914636</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10.4074422631405</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9.5000317170865</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9.161816018326284</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8.913627025534232</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8.799274107140054</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8.335508550897641</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8.275535183571314</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8.240447025363618</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8.216112360290072</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7.908005312866728</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7.788605641411273</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7.778152495954682</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.665195775009115</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.542073792847647</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7.378868840111597</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7.251568631278382</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>7.100437277067984</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>7.024423915842903</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6.73650542439198</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6.700222752642382</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6.679901416981338</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6.633690869228115</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>6.297195687875012</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6.232889988004143</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>6.078610417987562</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>6.073739126008116</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5.601896270963658</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>5.288815940683156</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5.245654095095698</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5.230808144247745</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5.104770821357429</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>5.104767181518222</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5.0586650418178</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.041536772765909</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>5.036408924477143</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>5.021573723728734</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4.924888436226138</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4.918913513107137</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>4.916023145354487</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4.916017807544448</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4.906387217105035</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4.904649436675812</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4.888685947150706</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4.831524459184777</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4.814396056530001</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4.813943547329491</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4.736889059669469</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>4.726224018944181</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4.722595506367155</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4.719857205414391</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4.71218879506925</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4.71218562740654</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>4.709263356205318</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>4.707771730101995</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4.698819438089386</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4.687572527072725</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>4.685691472398812</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>4.685687162808616</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>4.66920132972013</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4.604261815148614</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4.604259769292152</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4.495068884727083</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4.480265097013536</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>4.480258734680609</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>4.475571792297273</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4.460616354839297</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4.452695169918508</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4.452269003190401</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4.452265614177953</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>4.449494715575342</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>4.44672724950923</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4.446725358595804</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>4.432364585717341</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>4.418143663341567</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4.404089826112267</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4.38829151753326</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4.388291517533105</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>4.388291517533061</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>4.349633931007135</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>4.349633931007135</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>4.349633931007113</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>4.349633931007091</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>4.349633931006958</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>4.349633931006935</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>4.335477316788694</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>4.335475298823366</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>4.325966886632271</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>4.274519009916844</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>4.270257231299013</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>4.254097306094806</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>4.219071160432186</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>4.219070660454505</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>4.194067920212285</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>4.175848843858976</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>4.169529680102424</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>4.168261095111125</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>4.168259217128245</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>4.16099973736932</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>4.152707281016244</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>4.139113523896243</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>4.118046203630454</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>4.06111633755124</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>4.007972247591174</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>4.00000000000007</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>4.00000000000007</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>4.00000000000007</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/DashboardApp/hash_table.xlsx
+++ b/src/DashboardApp/hash_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,1446 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>22.86600961511795</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>18.83187548348985</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>18.6144625992209</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>17.02360507988341</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16.55407615166203</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>16.43512253136544</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>15.77900665531947</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>15.54531838293443</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>14.66410218309929</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>13.3447267903799</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>12.44995122914663</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10.65512917904204</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9.500031717086577</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9.16181601832664</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8.913627025534243</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8.335508550897774</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8.275535183571348</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8.254373206547704</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7.908005312866873</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7.788605641411117</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7.778152495954949</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7.665195775008982</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7.542073792847603</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7.378868840111763</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.251568631278382</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.100437277068083</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7.024423915842871</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>6.73650542439198</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6.679901416981259</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>6.338943322872359</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6.297195687874957</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6.232889988004087</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6.078610417987607</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6.073739126008116</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5.601896270963658</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5.288815940683255</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5.245654095095698</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>5.230808144247701</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5.104770821357563</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>5.104767181518222</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5.0586650418176</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5.041536772765931</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5.03640892447712</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>5.021573723728667</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.952326044590071</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4.924888436226138</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4.91891351310707</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4.916023145354398</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4.916017807544404</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4.906387217104968</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>4.904649436675812</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4.888685947150639</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4.831524459184755</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4.814396056529979</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4.813943547329447</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4.795308242662988</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4.736889059669314</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4.736883734731001</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4.726224018944181</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>4.722595506367155</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4.719857205414435</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4.71218879506925</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4.712185627406562</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4.707771730101995</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>4.687572527072725</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>4.685691472398901</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4.685687162808527</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4.669201329720174</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>4.604261815148591</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>4.604259769292196</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>4.49506888472706</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4.480265097013403</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4.475571792297295</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4.46061635483932</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4.452695169918464</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>4.452269003190468</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>4.452265614177953</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4.449494715575342</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4.446725358595827</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4.432364585717341</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4.418143663341567</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>4.404089826112356</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>4.349633931007113</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>4.349633931007091</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>4.335477316788561</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>4.335475298823388</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>4.325966886632249</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>4.274519009916911</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>4.270257231299013</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>4.254097306094673</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>4.233442504238094</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>4.219071160432186</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>4.219070660454505</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>4.194067920212374</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>4.175848843858931</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>4.169529680102513</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>4.168261095111214</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>4.168259217128245</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>4.16099973736932</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>4.152707281016221</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>4.139113523896243</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>4.11804620363041</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>4.061116337551218</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>4.00797224759124</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/DashboardApp/hash_table.xlsx
+++ b/src/DashboardApp/hash_table.xlsx
@@ -437,17 +437,17 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22.86600961511795</v>
+        <v>26.05845476919577</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>18.83187548348985</v>
+        <v>22.86600961511795</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>18.6144625992209</v>
+        <v>17.36819739724094</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +492,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10.65512917904204</v>
+        <v>10.40744226314052</v>
       </c>
     </row>
     <row r="14">
@@ -502,412 +502,412 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9.16181601832664</v>
+        <v>8.799274107140009</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>8.913627025534243</v>
+        <v>8.335508550897774</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>8.335508550897774</v>
+        <v>8.275535183571348</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8.275535183571348</v>
+        <v>8.254373206547704</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>8.254373206547704</v>
+        <v>8.240447025363707</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7.908005312866873</v>
+        <v>8.216112360289962</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7.788605641411117</v>
+        <v>7.908005312866873</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7.778152495954949</v>
+        <v>7.788605641411117</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7.665195775008982</v>
+        <v>7.778152495954949</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7.542073792847603</v>
+        <v>7.665195775008982</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>7.378868840111763</v>
+        <v>7.542073792847603</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7.251568631278382</v>
+        <v>7.378868840111763</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7.100437277068083</v>
+        <v>7.251568631278382</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7.024423915842871</v>
+        <v>7.100437277068083</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6.73650542439198</v>
+        <v>7.024423915842871</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6.679901416981259</v>
+        <v>6.73650542439198</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6.338943322872359</v>
+        <v>6.700222752642437</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6.297195687874957</v>
+        <v>6.679901416981259</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6.232889988004087</v>
+        <v>6.633690869228259</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6.078610417987607</v>
+        <v>6.297195687874957</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6.073739126008116</v>
+        <v>6.232889988004087</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5.601896270963658</v>
+        <v>6.078610417987607</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>5.288815940683255</v>
+        <v>6.073739126008116</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>5.245654095095698</v>
+        <v>5.601896270963658</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>5.230808144247701</v>
+        <v>5.288815940683255</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5.104770821357563</v>
+        <v>5.245654095095698</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>5.104767181518222</v>
+        <v>5.230808144247701</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>5.0586650418176</v>
+        <v>5.104770821357563</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>5.041536772765931</v>
+        <v>5.104767181518222</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>5.03640892447712</v>
+        <v>5.0586650418176</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>5.021573723728667</v>
+        <v>5.041536772765931</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>4.952326044590071</v>
+        <v>5.03640892447712</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4.924888436226138</v>
+        <v>5.021573723728667</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4.91891351310707</v>
+        <v>4.924888436226138</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>4.916023145354398</v>
+        <v>4.91891351310707</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4.916017807544404</v>
+        <v>4.916023145354398</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>4.906387217104968</v>
+        <v>4.916017807544404</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>4.904649436675812</v>
+        <v>4.906387217104968</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4.888685947150639</v>
+        <v>4.904649436675812</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>4.831524459184755</v>
+        <v>4.888685947150639</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4.814396056529979</v>
+        <v>4.831524459184755</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>4.813943547329447</v>
+        <v>4.814396056529979</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>4.795308242662988</v>
+        <v>4.813943547329447</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>4.736889059669314</v>
+        <v>4.795308242662988</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>4.736883734731001</v>
+        <v>4.736889059669314</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>4.726224018944181</v>
+        <v>4.736883734731001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>4.722595506367155</v>
+        <v>4.726224018944181</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>4.719857205414435</v>
+        <v>4.722595506367155</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4.71218879506925</v>
+        <v>4.719857205414435</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4.712185627406562</v>
+        <v>4.71218879506925</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4.707771730101995</v>
+        <v>4.712185627406562</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>4.687572527072725</v>
+        <v>4.70926335620534</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4.685691472398901</v>
+        <v>4.707771730101995</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>4.685687162808527</v>
+        <v>4.698819438089386</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>4.669201329720174</v>
+        <v>4.687572527072725</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4.604261815148591</v>
+        <v>4.685691472398901</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4.604259769292196</v>
+        <v>4.685687162808527</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4.49506888472706</v>
+        <v>4.669201329720174</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4.480265097013403</v>
+        <v>4.604261815148591</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4.475571792297295</v>
+        <v>4.604259769292196</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>4.46061635483932</v>
+        <v>4.49506888472706</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>4.452695169918464</v>
+        <v>4.480265097013403</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4.452269003190468</v>
+        <v>4.480258734680631</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>4.452265614177953</v>
+        <v>4.475571792297295</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4.449494715575342</v>
+        <v>4.46061635483932</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4.446725358595827</v>
+        <v>4.452695169918464</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>4.432364585717341</v>
+        <v>4.452269003190468</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4.418143663341567</v>
+        <v>4.452265614177953</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>4.404089826112356</v>
+        <v>4.449494715575342</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4.388291517533238</v>
+        <v>4.44672724950923</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4.388291517533216</v>
+        <v>4.446725358595827</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4.388291517533216</v>
+        <v>4.432364585717341</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4.388291517533216</v>
+        <v>4.418143663341567</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4.388291517533216</v>
+        <v>4.404089826112356</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4.388291517533194</v>
+        <v>4.38829151753326</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4.388291517533194</v>
+        <v>4.388291517533238</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>4.388291517533172</v>
+        <v>4.388291517533216</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4.388291517533172</v>
+        <v>4.388291517533216</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4.388291517533172</v>
+        <v>4.388291517533216</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>4.388291517533172</v>
+        <v>4.388291517533216</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4.388291517533172</v>
+        <v>4.388291517533194</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>4.388291517533172</v>
+        <v>4.388291517533194</v>
       </c>
     </row>
     <row r="97">
@@ -922,417 +922,417 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>4.388291517533149</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4.388291517533127</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4.349633931007113</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>4.349633931007091</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4.349633931007069</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>4.349633931007069</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>4.349633931007046</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>4.349633931007046</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>4.349633931007046</v>
+        <v>4.388291517533149</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>4.349633931007046</v>
+        <v>4.388291517533127</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>4.349633931007046</v>
+        <v>4.349633931007113</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>4.349633931007046</v>
+        <v>4.349633931007091</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>4.349633931007046</v>
+        <v>4.349633931007069</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>4.349633931007046</v>
+        <v>4.349633931007069</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>4.349633931007024</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>4.349633931007024</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>4.349633931007024</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>4.349633931007024</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>4.349633931007024</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>4.349633931007002</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>4.349633931007002</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>4.34963393100698</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>4.34963393100698</v>
+        <v>4.349633931007024</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>4.34963393100698</v>
+        <v>4.349633931007024</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>4.335477316788561</v>
+        <v>4.349633931007024</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>4.335475298823388</v>
+        <v>4.349633931007024</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>4.325966886632249</v>
+        <v>4.349633931007024</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>4.274519009916911</v>
+        <v>4.349633931007002</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>4.270257231299013</v>
+        <v>4.34963393100698</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>4.254097306094673</v>
+        <v>4.34963393100698</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>4.23344250423825</v>
+        <v>4.34963393100698</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>4.23344250423825</v>
+        <v>4.335477316788561</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>4.233442504238227</v>
+        <v>4.335475298823388</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>4.233442504238227</v>
+        <v>4.325966886632249</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>4.233442504238227</v>
+        <v>4.274519009916911</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>4.233442504238227</v>
+        <v>4.270257231299013</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>4.233442504238227</v>
+        <v>4.254097306094673</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>4.233442504238227</v>
+        <v>4.23344250423825</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>4.233442504238205</v>
+        <v>4.23344250423825</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>4.233442504238205</v>
+        <v>4.23344250423825</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>4.233442504238205</v>
+        <v>4.233442504238227</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>4.233442504238205</v>
+        <v>4.233442504238227</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>4.233442504238205</v>
+        <v>4.233442504238227</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>4.233442504238183</v>
+        <v>4.233442504238227</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>4.233442504238183</v>
+        <v>4.233442504238227</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>4.233442504238183</v>
+        <v>4.233442504238227</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>4.233442504238183</v>
+        <v>4.233442504238205</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>4.233442504238183</v>
+        <v>4.233442504238205</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>4.233442504238161</v>
+        <v>4.233442504238205</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>4.233442504238139</v>
+        <v>4.233442504238205</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>4.233442504238139</v>
+        <v>4.233442504238183</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>4.233442504238139</v>
+        <v>4.233442504238183</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>4.233442504238116</v>
+        <v>4.233442504238183</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>4.233442504238116</v>
+        <v>4.233442504238183</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>4.233442504238094</v>
+        <v>4.233442504238183</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>4.219071160432186</v>
+        <v>4.233442504238183</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>4.219070660454505</v>
+        <v>4.233442504238161</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>4.194067920212374</v>
+        <v>4.233442504238161</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>4.175848843858931</v>
+        <v>4.233442504238161</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>4.169529680102513</v>
+        <v>4.233442504238139</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>4.168261095111214</v>
+        <v>4.233442504238139</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>4.168259217128245</v>
+        <v>4.233442504238139</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>4.16099973736932</v>
+        <v>4.233442504238139</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>4.152707281016221</v>
+        <v>4.233442504238116</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>4.139113523896243</v>
+        <v>4.233442504238116</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>4.11804620363041</v>
+        <v>4.233442504238094</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>4.061116337551218</v>
+        <v>4.219071160432186</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>4.00797224759124</v>
+        <v>4.219070660454505</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>4.000000000000048</v>
+        <v>4.194067920212374</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>4.000000000000048</v>
+        <v>4.175848843858931</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>4.000000000000048</v>
+        <v>4.169529680102513</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>4.000000000000048</v>
+        <v>4.168261095111214</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>4.000000000000026</v>
+        <v>4.168259217128245</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>4.000000000000026</v>
+        <v>4.16099973736932</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>4.000000000000026</v>
+        <v>4.152707281016221</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>4.000000000000026</v>
+        <v>4.139113523896243</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>4.000000000000026</v>
+        <v>4.11804620363041</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>4.000000000000026</v>
+        <v>4.061116337551218</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>4.000000000000026</v>
+        <v>4.00797224759124</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>4.000000000000026</v>
+        <v>4.000000000000048</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>4.000000000000026</v>
+        <v>4.000000000000048</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>4.000000000000026</v>
+        <v>4.000000000000048</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>4.000000000000026</v>
+        <v>4.000000000000048</v>
       </c>
     </row>
     <row r="182">
@@ -1347,57 +1347,57 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>4.000000000000004</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>4.000000000000004</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>4.000000000000004</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>4.000000000000004</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>4.000000000000004</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>4.000000000000004</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>4.000000000000004</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>4.000000000000004</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>4.000000000000004</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>4.000000000000004</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>4.000000000000004</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="195">
@@ -1452,202 +1452,202 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>3.999999999999981</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>3.999999999999981</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>3.999999999999981</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>3.999999999999981</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>3.999999999999981</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>3.999999999999981</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>3.999999999999981</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>3.999999999999981</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>3.999999999999981</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>3.999999999999981</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>3.999999999999981</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>3.999999999999959</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3.999999999999959</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3.999999999999959</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>3.999999999999959</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>3.999999999999959</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>3.999999999999959</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3.999999999999959</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3.999999999999937</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3.999999999999937</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>3.999999999999937</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>3.999999999999937</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>-1</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>-1</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>-1</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>-1</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>-1</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>-1</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>-1</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>-1</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>-1</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>-1</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>-1</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>-1</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>-1</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>-1</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>-1</v>
+        <v>3.999999999999937</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>-1</v>
+        <v>3.999999999999937</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>-1</v>
+        <v>3.999999999999937</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>-1</v>
+        <v>3.999999999999937</v>
       </c>
     </row>
     <row r="245">

--- a/src/DashboardApp/hash_table.xlsx
+++ b/src/DashboardApp/hash_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,1446 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>22.86600961511795</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>21.64736113255699</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>17.02360507988341</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16.55407615166203</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16.43512253136544</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>15.77900665531947</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>15.54531838293443</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>14.66410218309929</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>13.3447267903799</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>12.44995122914663</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11.45377185083114</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9.500031717086577</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8.913627025534243</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8.799274107140009</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8.275535183571348</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8.240447025363707</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7.908005312866873</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7.788605641411117</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7.778152495954949</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7.665195775008982</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7.542073792847603</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7.378868840111763</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7.251568631278382</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7.100437277068083</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.024423915842871</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6.73650542439198</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6.700222752642437</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>6.679901416981259</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6.633690869228259</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>6.297195687874957</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6.232889988004087</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6.078610417987607</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6.073739126008116</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>5.601896270963658</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5.288815940683255</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5.245654095095698</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5.230808144247701</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>5.104770821357563</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5.104767181518222</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>5.0586650418176</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5.041536772765931</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5.03640892447712</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5.021573723728667</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4.924888436226138</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.916023145354398</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4.916017807544404</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4.906387217104968</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4.904649436675812</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4.888685947150639</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4.831524459184755</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>4.814396056529979</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4.726224018944181</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4.722595506367155</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4.71218879506925</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4.712185627406562</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4.70926335620534</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4.707771730101995</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4.687572527072725</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4.685691472398901</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>4.685687162808527</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4.669201329720174</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4.604261815148591</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4.604259769292196</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4.49506888472706</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>4.475571792297295</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>4.46061635483932</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4.452695169918464</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4.452269003190468</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>4.452265614177953</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>4.449494715575342</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>4.44672724950923</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4.446725358595827</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4.432364585717341</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4.429826105328005</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4.418143663341567</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>4.404089826112356</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>4.38829151753326</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>4.349633931007113</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>4.349633931007091</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>4.335477316788561</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>4.335475298823388</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>4.325966886632249</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>4.274519009916911</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>4.270257231299013</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>4.254097306094673</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>4.233442504238094</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>4.219071160432186</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>4.219070660454505</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>4.194067920212374</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>4.175848843858931</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>4.169529680102513</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>4.168261095111214</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>4.168259217128245</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>4.16099973736932</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>4.152707281016221</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>4.139113523896243</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>4.11804620363041</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>4.061116337551218</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>4.00797224759124</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
